--- a/typesafe-reporting/sortie/Impayes_30-90j_TypeSafe_demo.xlsx
+++ b/typesafe-reporting/sortie/Impayes_30-90j_TypeSafe_demo.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1954" uniqueCount="379">
   <si>
     <t>IMPAYÉS 30-90J · RETOURS GESTIONNAIRES · COUCHE TYPESAFE</t>
   </si>
@@ -119,12 +119,12 @@
     <t>À faire</t>
   </si>
   <si>
+    <t>En cours</t>
+  </si>
+  <si>
     <t>Restructuration</t>
   </si>
   <si>
-    <t>En cours</t>
-  </si>
-  <si>
     <t>Escalade contentieux</t>
   </si>
   <si>
@@ -179,7 +179,7 @@
     <t>• 27 dossiers sur 30 ont un commentaire gestionnaire ; 3 restent sans retour.</t>
   </si>
   <si>
-    <t>• 11 dossiers partent en revue analyste (confiance faible ou incohérence) : aucune décision automatique.</t>
+    <t>• 10 dossiers partent en revue analyste (confiance faible ou incohérence) : aucune décision automatique.</t>
   </si>
   <si>
     <t>• 3 promesses de règlement tombent après la date de bascule en douteux.</t>
@@ -326,7 +326,7 @@
     <t>Promesse de règlement d'ici 10 jours, pas d'autre information.</t>
   </si>
   <si>
-    <t>nature de l'entité incertaine (0.45)</t>
+    <t>nature de l'entité incertaine (0.47)</t>
   </si>
   <si>
     <t>LD9000008</t>
@@ -356,7 +356,7 @@
     <t>Décès du gérant le mois dernier, la succession est en cours. Les héritiers n'ont pas encore été reçus.</t>
   </si>
   <si>
-    <t>statut incertain (0.40)</t>
+    <t>statut incertain (0.44)</t>
   </si>
   <si>
     <t>LD9000010</t>
@@ -416,7 +416,7 @@
     <t>Hospitalisation du client, reprise du travail prévue en novembre. L'épouse s'engage à verser le 20 octobre.</t>
   </si>
   <si>
-    <t>crédibilité incertaine (0.21)</t>
+    <t>crédibilité incertaine (0.31)</t>
   </si>
   <si>
     <t>LD9000016</t>
@@ -428,6 +428,9 @@
     <t>Domiciliation de la subvention annuelle confirmée par la tutelle, virement attendu cette semaine.</t>
   </si>
   <si>
+    <t>statut incertain (0.37)</t>
+  </si>
+  <si>
     <t>LD9000017</t>
   </si>
   <si>
@@ -458,7 +461,7 @@
     <t>Le client attend le paiement d'une créance sur une société du groupe. Aucune date donnée.</t>
   </si>
   <si>
-    <t>motif incertain (0.34)</t>
+    <t>motif incertain (0.36)</t>
   </si>
   <si>
     <t>LD9000020</t>
@@ -512,18 +515,12 @@
     <t>FAYE OUMAR</t>
   </si>
   <si>
-    <t>statut incertain (0.54)</t>
-  </si>
-  <si>
     <t>LD9000027</t>
   </si>
   <si>
     <t>KANE KHADY</t>
   </si>
   <si>
-    <t>nature de l'entité incertaine (0.49)</t>
-  </si>
-  <si>
     <t>LD9000028</t>
   </si>
   <si>
@@ -614,10 +611,10 @@
     <t>Contrepartie intra-groupe : traitement spécifique</t>
   </si>
   <si>
-    <t>Revue : nature de l'entité incertaine (0.45)</t>
-  </si>
-  <si>
-    <t>Revue : statut incertain (0.40)</t>
+    <t>Revue : nature de l'entité incertaine (0.47)</t>
+  </si>
+  <si>
+    <t>Revue : statut incertain (0.44)</t>
   </si>
   <si>
     <t>Date promise 27 j après la bascule en douteux</t>
@@ -626,19 +623,19 @@
     <t>Segment « Consumer » douteux au vu du nom</t>
   </si>
   <si>
-    <t>Date lue par le code mais promesse jugée vague</t>
-  </si>
-  <si>
     <t>Segment « Commercial » douteux au vu du nom</t>
   </si>
   <si>
     <t>Revue : statut incertain (0.50)</t>
   </si>
   <si>
-    <t>Revue : crédibilité incertaine (0.21)</t>
-  </si>
-  <si>
-    <t>Revue : motif incertain (0.34)</t>
+    <t>Revue : crédibilité incertaine (0.31)</t>
+  </si>
+  <si>
+    <t>Revue : statut incertain (0.37)</t>
+  </si>
+  <si>
+    <t>Revue : motif incertain (0.36)</t>
   </si>
   <si>
     <t>Commentaire vide : relancer le gestionnaire</t>
@@ -647,12 +644,6 @@
     <t>Date promise 42 j après la bascule en douteux</t>
   </si>
   <si>
-    <t>Revue : statut incertain (0.54)</t>
-  </si>
-  <si>
-    <t>Revue : nature de l'entité incertaine (0.49)</t>
-  </si>
-  <si>
     <t>MÉTHODOLOGIE ET PISTE D'AUDIT</t>
   </si>
   <si>
@@ -749,7 +740,7 @@
     <t>genere</t>
   </si>
   <si>
-    <t>2026-10-03T10:08:18</t>
+    <t>2026-10-03T10:19:53</t>
   </si>
   <si>
     <t>nature_entite</t>
@@ -761,7 +752,7 @@
     <t>parapublique</t>
   </si>
   <si>
-    <t>{"parapublique": 1.0, "particulier": 0.0, "privee": 0.0, "publique": 0.0}</t>
+    <t>{"particulier": 0.0, "parapublique": 1.0, "publique": 0.0, "privee": 0.0}</t>
   </si>
   <si>
     <t>intra_groupe</t>
@@ -782,7 +773,7 @@
     <t>retard_technique</t>
   </si>
   <si>
-    <t>{"litige_juridique": 0.0, "aucun_motif": 0.0, "sante_deces": 0.0, "tension_tresorerie": 0.01, "perte_revenus": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "retard_technique": 0.93, "regularisation_annoncee": 0.06}</t>
+    <t>{"retard_technique": 0.92, "sante_deces": 0.0, "client_injoignable": 0.0, "tension_tresorerie": 0.01, "fraude_detournement": 0.0, "perte_revenus": 0.0, "aucun_motif": 0.0, "litige_juridique": 0.0, "regularisation_annoncee": 0.07}</t>
   </si>
   <si>
     <t>promesse_datee</t>
@@ -806,118 +797,121 @@
     <t>promesse_reglement</t>
   </si>
   <si>
-    <t>{"a_faire": 0.0, "regularise_a_verifier": 0.1, "escalade_contentieux": 0.0, "promesse_reglement": 0.9, "restructuration": 0.0, "en_cours": 0.0}</t>
+    <t>{"restructuration": 0.0, "en_cours": 0.0, "a_faire": 0.0, "regularise_a_verifier": 0.21, "escalade_contentieux": 0.0, "promesse_reglement": 0.79}</t>
   </si>
   <si>
     <t>publique</t>
   </si>
   <si>
-    <t>{"parapublique": 0.0, "particulier": 0.0, "publique": 1.0, "privee": 0.0}</t>
+    <t>{"particulier": 0.0, "parapublique": 0.0, "privee": 0.0, "publique": 1.0}</t>
   </si>
   <si>
     <t>tension_tresorerie</t>
   </si>
   <si>
-    <t>{"client_injoignable": 0.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.68, "litige_juridique": 0.0, "retard_technique": 0.32, "regularisation_annoncee": 0.0, "perte_revenus": 0.0, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.0, "1": 0.0, "2": 0.06, "3": 0.26, "4": 0.68}</t>
-  </si>
-  <si>
-    <t>{"escalade_contentieux": 0.0, "a_faire": 0.0, "promesse_reglement": 0.95, "en_cours": 0.03, "restructuration": 0.0, "regularise_a_verifier": 0.02}</t>
+    <t>{"client_injoignable": 0.0, "sante_deces": 0.0, "regularisation_annoncee": 0.0, "retard_technique": 0.36, "perte_revenus": 0.0, "litige_juridique": 0.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.64}</t>
+  </si>
+  <si>
+    <t>{"0": 0.0, "1": 0.0, "2": 0.07, "3": 0.28, "4": 0.65}</t>
+  </si>
+  <si>
+    <t>{"en_cours": 0.03, "promesse_reglement": 0.95, "a_faire": 0.0, "restructuration": 0.0, "escalade_contentieux": 0.0, "regularise_a_verifier": 0.02}</t>
+  </si>
+  <si>
+    <t>{"privee": 0.0, "particulier": 0.0, "publique": 1.0, "parapublique": 0.0}</t>
   </si>
   <si>
     <t>client_injoignable</t>
   </si>
   <si>
-    <t>{"aucun_motif": 0.0, "retard_technique": 0.0, "perte_revenus": 0.0, "litige_juridique": 0.0, "sante_deces": 0.0, "client_injoignable": 1.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0, "regularisation_annoncee": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.81, "1": 0.19, "2": 0.0, "3": 0.0, "4": 0.0}</t>
+    <t>{"regularisation_annoncee": 0.0, "aucun_motif": 0.0, "litige_juridique": 0.0, "retard_technique": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0, "perte_revenus": 0.0, "client_injoignable": 1.0, "sante_deces": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.83, "1": 0.17, "2": 0.0, "3": 0.0, "4": 0.0}</t>
   </si>
   <si>
     <t>en_cours</t>
   </si>
   <si>
-    <t>{"en_cours": 0.73, "escalade_contentieux": 0.26, "restructuration": 0.0, "regularise_a_verifier": 0.0, "a_faire": 0.01, "promesse_reglement": 0.0}</t>
-  </si>
-  <si>
-    <t>{"privee": 0.0, "publique": 0.02, "particulier": 0.0, "parapublique": 0.98}</t>
+    <t>{"a_faire": 0.01, "promesse_reglement": 0.0, "restructuration": 0.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.31, "en_cours": 0.68}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.99, "publique": 0.01, "privee": 0.0, "particulier": 0.0}</t>
   </si>
   <si>
     <t>regularisation_annoncee</t>
   </si>
   <si>
-    <t>{"client_injoignable": 0.0, "retard_technique": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "perte_revenus": 0.0, "regularisation_annoncee": 0.99, "fraude_detournement": 0.0, "aucun_motif": 0.01, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.18, "1": 0.82, "2": 0.0, "3": 0.0, "4": 0.0}</t>
+    <t>{"client_injoignable": 0.0, "sante_deces": 0.0, "tension_tresorerie": 0.0, "regularisation_annoncee": 0.99, "aucun_motif": 0.01, "retard_technique": 0.0, "perte_revenus": 0.0, "litige_juridique": 0.0, "fraude_detournement": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.21, "1": 0.79, "2": 0.0, "3": 0.0, "4": 0.0}</t>
   </si>
   <si>
     <t>regularise_a_verifier</t>
   </si>
   <si>
-    <t>{"escalade_contentieux": 0.0, "regularise_a_verifier": 1.0, "a_faire": 0.0, "en_cours": 0.0, "promesse_reglement": 0.0, "restructuration": 0.0}</t>
+    <t>{"restructuration": 0.0, "a_faire": 0.0, "promesse_reglement": 0.0, "regularise_a_verifier": 1.0, "escalade_contentieux": 0.0, "en_cours": 0.0}</t>
   </si>
   <si>
     <t>privee</t>
   </si>
   <si>
-    <t>{"privee": 0.99, "parapublique": 0.01, "particulier": 0.0, "publique": 0.0}</t>
+    <t>{"parapublique": 0.01, "privee": 0.99, "publique": 0.0, "particulier": 0.0}</t>
   </si>
   <si>
     <t>perte_revenus</t>
   </si>
   <si>
-    <t>{"client_injoignable": 0.0, "aucun_motif": 0.0, "retard_technique": 0.01, "perte_revenus": 0.99, "fraude_detournement": 0.0, "regularisation_annoncee": 0.0, "sante_deces": 0.0, "litige_juridique": 0.0, "tension_tresorerie": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.04, "1": 0.76, "2": 0.08, "3": 0.12, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"promesse_reglement": 1.0, "a_faire": 0.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.0, "en_cours": 0.0, "restructuration": 0.0}</t>
-  </si>
-  <si>
-    <t>{"parapublique": 0.0, "privee": 1.0, "publique": 0.0, "particulier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"tension_tresorerie": 0.0, "aucun_motif": 0.0, "retard_technique": 0.0, "perte_revenus": 1.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.0, "litige_juridique": 0.0, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.15, "1": 0.85, "2": 0.0, "3": 0.0, "4": 0.0}</t>
+    <t>{"tension_tresorerie": 0.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "perte_revenus": 1.0, "client_injoignable": 0.0, "retard_technique": 0.0, "regularisation_annoncee": 0.0, "litige_juridique": 0.0, "sante_deces": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.04, "1": 0.8, "2": 0.06, "3": 0.1, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"en_cours": 0.0, "restructuration": 0.0, "a_faire": 0.0, "escalade_contentieux": 0.0, "regularise_a_verifier": 0.0, "promesse_reglement": 1.0}</t>
+  </si>
+  <si>
+    <t>{"privee": 1.0, "parapublique": 0.0, "particulier": 0.0, "publique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"sante_deces": 0.0, "tension_tresorerie": 0.0, "client_injoignable": 0.0, "regularisation_annoncee": 0.0, "fraude_detournement": 0.0, "perte_revenus": 1.0, "aucun_motif": 0.0, "retard_technique": 0.0, "litige_juridique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.16, "1": 0.84, "2": 0.0, "3": 0.0, "4": 0.0}</t>
   </si>
   <si>
     <t>restructuration</t>
   </si>
   <si>
-    <t>{"en_cours": 0.0, "restructuration": 1.0, "a_faire": 0.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.0, "promesse_reglement": 0.0}</t>
+    <t>{"promesse_reglement": 0.0, "en_cours": 0.0, "a_faire": 0.0, "escalade_contentieux": 0.0, "restructuration": 1.0, "regularise_a_verifier": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.02, "1": 0.98, "2": 0.0, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"en_cours": 0.0, "escalade_contentieux": 0.0, "a_faire": 0.0, "promesse_reglement": 1.0, "restructuration": 0.0, "regularise_a_verifier": 0.0}</t>
   </si>
   <si>
     <t>particulier</t>
   </si>
   <si>
-    <t>{"particulier": 0.59, "privee": 0.41, "parapublique": 0.0, "publique": 0.0}</t>
+    <t>{"parapublique": 0.0, "particulier": 0.6, "publique": 0.0, "privee": 0.4}</t>
   </si>
   <si>
     <t>aucun_motif</t>
   </si>
   <si>
-    <t>{"regularisation_annoncee": 0.01, "perte_revenus": 0.0, "fraude_detournement": 0.0, "litige_juridique": 0.0, "aucun_motif": 0.93, "retard_technique": 0.0, "sante_deces": 0.0, "client_injoignable": 0.0, "tension_tresorerie": 0.06}</t>
-  </si>
-  <si>
-    <t>{"0": 0.02, "1": 0.98, "2": 0.0, "3": 0.0, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"escalade_contentieux": 0.0, "a_faire": 0.0, "regularise_a_verifier": 0.0, "en_cours": 0.0, "promesse_reglement": 1.0, "restructuration": 0.0}</t>
-  </si>
-  <si>
-    <t>{"parapublique": 0.0, "particulier": 1.0, "publique": 0.0, "privee": 0.0}</t>
+    <t>{"perte_revenus": 0.0, "client_injoignable": 0.0, "litige_juridique": 0.0, "sante_deces": 0.0, "aucun_motif": 0.93, "tension_tresorerie": 0.05, "retard_technique": 0.01, "fraude_detournement": 0.0, "regularisation_annoncee": 0.01}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.0, "publique": 0.0, "privee": 0.0, "particulier": 1.0}</t>
   </si>
   <si>
     <t>litige_juridique</t>
   </si>
   <si>
-    <t>{"perte_revenus": 0.0, "client_injoignable": 0.0, "litige_juridique": 1.0, "sante_deces": 0.0, "aucun_motif": 0.0, "tension_tresorerie": 0.0, "retard_technique": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.0}</t>
+    <t>{"tension_tresorerie": 0.0, "perte_revenus": 0.0, "sante_deces": 0.0, "litige_juridique": 1.0, "client_injoignable": 0.0, "aucun_motif": 0.0, "regularisation_annoncee": 0.0, "retard_technique": 0.0, "fraude_detournement": 0.0}</t>
   </si>
   <si>
     <t>{"0": 0.99, "1": 0.01, "2": 0.0, "3": 0.0, "4": 0.0}</t>
@@ -926,34 +920,40 @@
     <t>escalade_contentieux</t>
   </si>
   <si>
-    <t>{"a_faire": 0.0, "en_cours": 0.01, "escalade_contentieux": 0.99, "restructuration": 0.0, "promesse_reglement": 0.0, "regularise_a_verifier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"particulier": 0.8, "publique": 0.0, "privee": 0.2, "parapublique": 0.0}</t>
+    <t>{"en_cours": 0.01, "a_faire": 0.0, "escalade_contentieux": 0.99, "regularise_a_verifier": 0.0, "restructuration": 0.0, "promesse_reglement": 0.0}</t>
+  </si>
+  <si>
+    <t>{"privee": 0.24, "parapublique": 0.0, "particulier": 0.76, "publique": 0.0}</t>
   </si>
   <si>
     <t>sante_deces</t>
   </si>
   <si>
-    <t>{"retard_technique": 0.0, "sante_deces": 1.0, "client_injoignable": 0.0, "tension_tresorerie": 0.0, "fraude_detournement": 0.0, "perte_revenus": 0.0, "aucun_motif": 0.0, "litige_juridique": 0.0, "regularisation_annoncee": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.79, "1": 0.17, "2": 0.04, "3": 0.0, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"restructuration": 0.0, "en_cours": 0.51, "a_faire": 0.2, "escalade_contentieux": 0.29, "regularise_a_verifier": 0.0, "promesse_reglement": 0.0}</t>
-  </si>
-  <si>
-    <t>{"privee": 1.0, "parapublique": 0.0, "publique": 0.0, "particulier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 0.0, "sante_deces": 0.0, "litige_juridique": 0.0, "aucun_motif": 0.0, "perte_revenus": 0.0, "retard_technique": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 1.0, "regularisation_annoncee": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.0, "1": 0.02, "2": 0.17, "3": 0.52, "4": 0.29}</t>
-  </si>
-  <si>
-    <t>{"promesse_reglement": 0.95, "a_faire": 0.0, "en_cours": 0.0, "restructuration": 0.05, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.0}</t>
+    <t>{"client_injoignable": 0.0, "sante_deces": 1.0, "litige_juridique": 0.0, "aucun_motif": 0.0, "perte_revenus": 0.0, "retard_technique": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0, "regularisation_annoncee": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.76, "1": 0.19, "2": 0.05, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"promesse_reglement": 0.0, "regularise_a_verifier": 0.0, "en_cours": 0.53, "restructuration": 0.01, "a_faire": 0.18, "escalade_contentieux": 0.28}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.0, "particulier": 0.0, "publique": 0.0, "privee": 1.0}</t>
+  </si>
+  <si>
+    <t>{"perte_revenus": 0.0, "client_injoignable": 0.0, "litige_juridique": 0.0, "sante_deces": 0.0, "aucun_motif": 0.0, "tension_tresorerie": 1.0, "fraude_detournement": 0.0, "retard_technique": 0.0, "regularisation_annoncee": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.0, "1": 0.03, "2": 0.16, "3": 0.52, "4": 0.29}</t>
+  </si>
+  <si>
+    <t>{"a_faire": 0.0, "escalade_contentieux": 0.0, "en_cours": 0.0, "restructuration": 0.04, "promesse_reglement": 0.96, "regularise_a_verifier": 0.0}</t>
+  </si>
+  <si>
+    <t>{"particulier": 0.0, "publique": 0.0, "parapublique": 0.01, "privee": 0.99}</t>
+  </si>
+  <si>
+    <t>{"fraude_detournement": 0.0, "aucun_motif": 1.0, "perte_revenus": 0.0, "retard_technique": 0.0, "client_injoignable": 0.0, "regularisation_annoncee": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "sante_deces": 0.0}</t>
   </si>
   <si>
     <t>{"0": 1.0, "1": 0.0, "2": 0.0, "3": 0.0, "4": 0.0}</t>
@@ -962,205 +962,202 @@
     <t>a_faire</t>
   </si>
   <si>
-    <t>{"escalade_contentieux": 0.01, "regularise_a_verifier": 0.0, "a_faire": 0.99, "promesse_reglement": 0.0, "en_cours": 0.0, "restructuration": 0.0}</t>
-  </si>
-  <si>
-    <t>{"privee": 0.99, "publique": 0.0, "particulier": 0.0, "parapublique": 0.01}</t>
-  </si>
-  <si>
-    <t>{"sante_deces": 0.0, "retard_technique": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "perte_revenus": 0.0, "regularisation_annoncee": 0.0, "fraude_detournement": 0.0, "aucun_motif": 1.0, "client_injoignable": 0.0}</t>
-  </si>
-  <si>
-    <t>{"restructuration": 0.0, "promesse_reglement": 0.0, "escalade_contentieux": 0.0, "a_faire": 0.01, "en_cours": 0.0, "regularise_a_verifier": 0.99}</t>
-  </si>
-  <si>
-    <t>{"parapublique": 0.0, "publique": 0.0, "particulier": 1.0, "privee": 0.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 0.0, "perte_revenus": 0.0, "regularisation_annoncee": 0.17, "aucun_motif": 0.83, "tension_tresorerie": 0.0, "sante_deces": 0.0, "litige_juridique": 0.0, "retard_technique": 0.0, "fraude_detournement": 0.0}</t>
-  </si>
-  <si>
-    <t>{"particulier": 0.0, "parapublique": 0.04, "publique": 0.0, "privee": 0.96}</t>
+    <t>{"promesse_reglement": 0.0, "a_faire": 0.98, "escalade_contentieux": 0.02, "regularise_a_verifier": 0.0, "restructuration": 0.0, "en_cours": 0.0}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.0, "particulier": 1.0, "privee": 0.0, "publique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"aucun_motif": 0.8200000000000001, "client_injoignable": 0.0, "fraude_detournement": 0.0, "retard_technique": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "regularisation_annoncee": 0.18, "perte_revenus": 0.0, "sante_deces": 0.0}</t>
+  </si>
+  <si>
+    <t>{"a_faire": 0.02, "escalade_contentieux": 0.0, "regularise_a_verifier": 0.98, "restructuration": 0.0, "en_cours": 0.0, "promesse_reglement": 0.0}</t>
   </si>
   <si>
     <t>fraude_detournement</t>
   </si>
   <si>
-    <t>{"retard_technique": 0.0, "sante_deces": 0.0, "client_injoignable": 0.0, "tension_tresorerie": 0.0, "fraude_detournement": 1.0, "perte_revenus": 0.0, "aucun_motif": 0.0, "litige_juridique": 0.0, "regularisation_annoncee": 0.0}</t>
-  </si>
-  <si>
-    <t>{"restructuration": 0.0, "en_cours": 0.0, "a_faire": 0.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 1.0, "promesse_reglement": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.02, "1": 0.97, "2": 0.0, "3": 0.01, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"a_faire": 0.0, "promesse_reglement": 0.41, "restructuration": 0.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.0, "en_cours": 0.59}</t>
-  </si>
-  <si>
-    <t>{"privee": 0.0, "particulier": 0.0, "publique": 0.11, "parapublique": 0.89}</t>
-  </si>
-  <si>
-    <t>{"regularisation_annoncee": 0.06, "aucun_motif": 0.87, "litige_juridique": 0.0, "retard_technique": 0.02, "fraude_detournement": 0.0, "tension_tresorerie": 0.05, "perte_revenus": 0.0, "client_injoignable": 0.0, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"parapublique": 0.0, "publique": 0.0, "particulier": 0.0, "privee": 1.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 0.0, "perte_revenus": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "sante_deces": 1.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.0, "retard_technique": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.0, "1": 0.45, "2": 0.16, "3": 0.39, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"escalade_contentieux": 0.0, "en_cours": 0.01, "restructuration": 0.0, "regularise_a_verifier": 0.0, "promesse_reglement": 0.99, "a_faire": 0.0}</t>
-  </si>
-  <si>
-    <t>{"particulier": 0.91, "privee": 0.04, "publique": 0.04, "parapublique": 0.01}</t>
-  </si>
-  <si>
-    <t>{"fraude_detournement": 0.0, "retard_technique": 0.87, "perte_revenus": 0.0, "regularisation_annoncee": 0.0, "client_injoignable": 0.0, "tension_tresorerie": 0.13, "litige_juridique": 0.0, "sante_deces": 0.0, "aucun_motif": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.0, "1": 0.0, "2": 0.11, "3": 0.69, "4": 0.2}</t>
-  </si>
-  <si>
-    <t>{"en_cours": 0.15, "escalade_contentieux": 0.0, "restructuration": 0.0, "promesse_reglement": 0.59, "regularise_a_verifier": 0.26, "a_faire": 0.0}</t>
-  </si>
-  <si>
-    <t>{"publique": 0.0, "particulier": 1.0, "privee": 0.0, "parapublique": 0.0}</t>
-  </si>
-  <si>
-    <t>{"aucun_motif": 0.86, "retard_technique": 0.0, "regularisation_annoncee": 0.0, "tension_tresorerie": 0.14, "sante_deces": 0.0, "litige_juridique": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "perte_revenus": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.21, "1": 0.75, "2": 0.04, "3": 0.0, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"escalade_contentieux": 0.0, "a_faire": 0.0, "promesse_reglement": 0.0, "en_cours": 0.0, "restructuration": 1.0, "regularise_a_verifier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"publique": 0.0, "particulier": 0.0, "parapublique": 0.0, "privee": 1.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 0.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "retard_technique": 1.0, "regularisation_annoncee": 0.0, "perte_revenus": 0.0, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.07, "1": 0.88, "2": 0.05, "3": 0.0, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"regularise_a_verifier": 0.05, "a_faire": 0.0, "promesse_reglement": 0.0, "en_cours": 0.95, "restructuration": 0.0, "escalade_contentieux": 0.0}</t>
-  </si>
-  <si>
-    <t>{"privee": 0.07, "particulier": 0.0, "publique": 0.06, "parapublique": 0.87}</t>
-  </si>
-  <si>
-    <t>{"regularisation_annoncee": 0.0, "tension_tresorerie": 0.42, "litige_juridique": 0.05, "retard_technique": 0.19, "fraude_detournement": 0.0, "aucun_motif": 0.34, "perte_revenus": 0.0, "client_injoignable": 0.0, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.22, "1": 0.45, "2": 0.33, "3": 0.0, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"a_faire": 0.25, "promesse_reglement": 0.0, "restructuration": 0.0, "regularise_a_verifier": 0.01, "en_cours": 0.72, "escalade_contentieux": 0.02}</t>
-  </si>
-  <si>
-    <t>{"particulier": 0.0, "privee": 0.0, "parapublique": 0.0, "publique": 1.0}</t>
+    <t>{"aucun_motif": 0.0, "litige_juridique": 0.0, "tension_tresorerie": 0.0, "retard_technique": 0.0, "client_injoignable": 0.0, "regularisation_annoncee": 0.0, "sante_deces": 0.0, "perte_revenus": 0.0, "fraude_detournement": 1.0}</t>
+  </si>
+  <si>
+    <t>{"promesse_reglement": 0.0, "regularise_a_verifier": 0.0, "a_faire": 0.0, "escalade_contentieux": 1.0, "restructuration": 0.0, "en_cours": 0.0}</t>
+  </si>
+  <si>
+    <t>{"publique": 0.0, "particulier": 0.0, "parapublique": 0.05, "privee": 0.95}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.9, "privee": 0.0, "publique": 0.1, "particulier": 0.0}</t>
+  </si>
+  <si>
+    <t>{"sante_deces": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.05, "tension_tresorerie": 0.07, "client_injoignable": 0.0, "perte_revenus": 0.0, "aucun_motif": 0.85, "litige_juridique": 0.0, "retard_technique": 0.03}</t>
+  </si>
+  <si>
+    <t>{"0": 0.01, "1": 0.98, "2": 0.0, "3": 0.01, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"en_cours": 0.59, "promesse_reglement": 0.41, "escalade_contentieux": 0.0, "restructuration": 0.0, "a_faire": 0.0, "regularise_a_verifier": 0.0}</t>
+  </si>
+  <si>
+    <t>{"perte_revenus": 0.0, "client_injoignable": 0.0, "litige_juridique": 0.0, "tension_tresorerie": 0.0, "aucun_motif": 0.0, "sante_deces": 1.0, "fraude_detournement": 0.0, "retard_technique": 0.0, "regularisation_annoncee": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.0, "1": 0.32, "2": 0.18, "3": 0.5, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"restructuration": 0.0, "a_faire": 0.0, "escalade_contentieux": 0.0, "promesse_reglement": 0.99, "en_cours": 0.01, "regularise_a_verifier": 0.0}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.01, "publique": 0.04, "privee": 0.04, "particulier": 0.91}</t>
+  </si>
+  <si>
+    <t>{"tension_tresorerie": 0.13, "client_injoignable": 0.0, "sante_deces": 0.0, "litige_juridique": 0.0, "perte_revenus": 0.0, "aucun_motif": 0.0, "retard_technique": 0.87, "regularisation_annoncee": 0.0, "fraude_detournement": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.0, "1": 0.0, "2": 0.11, "3": 0.62, "4": 0.27}</t>
+  </si>
+  <si>
+    <t>{"en_cours": 0.15, "a_faire": 0.0, "escalade_contentieux": 0.0, "restructuration": 0.0, "regularise_a_verifier": 0.36, "promesse_reglement": 0.49}</t>
+  </si>
+  <si>
+    <t>{"publique": 0.0, "particulier": 0.99, "parapublique": 0.0, "privee": 0.01}</t>
+  </si>
+  <si>
+    <t>{"retard_technique": 0.0, "litige_juridique": 0.0, "tension_tresorerie": 0.16, "aucun_motif": 0.84, "client_injoignable": 0.0, "regularisation_annoncee": 0.0, "sante_deces": 0.0, "perte_revenus": 0.0, "fraude_detournement": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.19, "1": 0.78, "2": 0.03, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"en_cours": 0.0, "promesse_reglement": 0.0, "a_faire": 0.0, "restructuration": 1.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.0}</t>
+  </si>
+  <si>
+    <t>{"particulier": 0.0, "privee": 1.0, "parapublique": 0.0, "publique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"sante_deces": 0.0, "perte_revenus": 0.0, "litige_juridique": 0.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "retard_technique": 1.0, "regularisation_annoncee": 0.0, "client_injoignable": 0.0, "tension_tresorerie": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.08, "1": 0.87, "2": 0.05, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"escalade_contentieux": 0.0, "a_faire": 0.0, "regularise_a_verifier": 0.06, "en_cours": 0.94, "promesse_reglement": 0.0, "restructuration": 0.0}</t>
+  </si>
+  <si>
+    <t>{"a_faire": 0.24, "en_cours": 0.72, "escalade_contentieux": 0.02, "promesse_reglement": 0.01, "restructuration": 0.0, "regularise_a_verifier": 0.01}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.86, "particulier": 0.0, "privee": 0.07, "publique": 0.07}</t>
+  </si>
+  <si>
+    <t>{"litige_juridique": 0.06, "aucun_motif": 0.32, "sante_deces": 0.0, "tension_tresorerie": 0.44, "perte_revenus": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "retard_technique": 0.18, "regularisation_annoncee": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.22, "1": 0.48, "2": 0.3, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"publique": 1.0, "particulier": 0.0, "parapublique": 0.0, "privee": 0.0}</t>
   </si>
   <si>
     <t>{"publique": 0.0, "privee": 0.0, "parapublique": 0.0, "particulier": 1.0}</t>
   </si>
   <si>
-    <t>{"particulier": 1.0, "parapublique": 0.0, "privee": 0.0, "publique": 0.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 0.0, "sante_deces": 0.0, "regularisation_annoncee": 0.0, "tension_tresorerie": 1.0, "aucun_motif": 0.0, "perte_revenus": 0.0, "fraude_detournement": 0.0, "retard_technique": 0.0, "litige_juridique": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.0, "1": 0.0, "2": 0.14, "3": 0.86, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"restructuration": 0.0, "regularise_a_verifier": 0.0, "en_cours": 0.0, "escalade_contentieux": 0.0, "a_faire": 0.0, "promesse_reglement": 1.0}</t>
-  </si>
-  <si>
-    <t>{"privee": 0.93, "parapublique": 0.05, "publique": 0.02, "particulier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"sante_deces": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.0, "tension_tresorerie": 0.0, "client_injoignable": 0.0, "perte_revenus": 0.0, "retard_technique": 1.0, "litige_juridique": 0.0, "aucun_motif": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.0, "1": 0.01, "2": 0.18, "3": 0.81, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"en_cours": 0.27, "promesse_reglement": 0.73, "escalade_contentieux": 0.0, "restructuration": 0.0, "a_faire": 0.0, "regularise_a_verifier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"parapublique": 0.0, "publique": 0.0, "privee": 1.0, "particulier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"tension_tresorerie": 0.02, "regularisation_annoncee": 0.11, "sante_deces": 0.0, "litige_juridique": 0.0, "retard_technique": 0.85, "aucun_motif": 0.02, "client_injoignable": 0.0, "perte_revenus": 0.0, "fraude_detournement": 0.0}</t>
+    <t>{"privee": 1.0, "particulier": 0.0, "publique": 0.0, "parapublique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"privee": 0.0, "parapublique": 0.0, "publique": 0.0, "particulier": 1.0}</t>
+  </si>
+  <si>
+    <t>{"sante_deces": 0.0, "retard_technique": 0.0, "aucun_motif": 0.0, "tension_tresorerie": 1.0, "litige_juridique": 0.0, "client_injoignable": 0.0, "regularisation_annoncee": 0.0, "fraude_detournement": 0.0, "perte_revenus": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.0, "1": 0.0, "2": 0.13, "3": 0.87, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"a_faire": 0.0, "escalade_contentieux": 0.0, "en_cours": 0.0, "regularise_a_verifier": 0.0, "restructuration": 0.0, "promesse_reglement": 1.0}</t>
+  </si>
+  <si>
+    <t>{"perte_revenus": 0.0, "regularisation_annoncee": 0.0, "aucun_motif": 0.0, "retard_technique": 1.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0, "sante_deces": 0.0, "litige_juridique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.0, "1": 0.01, "2": 0.22, "3": 0.77, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"escalade_contentieux": 0.0, "a_faire": 0.0, "en_cours": 0.31, "regularise_a_verifier": 0.0, "promesse_reglement": 0.6900000000000001, "restructuration": 0.0}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.06, "particulier": 0.0, "publique": 0.02, "privee": 0.92}</t>
+  </si>
+  <si>
+    <t>{"restructuration": 0.0, "promesse_reglement": 0.76, "escalade_contentieux": 0.0, "en_cours": 0.0, "a_faire": 0.0, "regularise_a_verifier": 0.24}</t>
+  </si>
+  <si>
+    <t>{"publique": 0.0, "parapublique": 0.0, "particulier": 0.0, "privee": 1.0}</t>
+  </si>
+  <si>
+    <t>{"litige_juridique": 0.0, "retard_technique": 0.84, "aucun_motif": 0.01, "sante_deces": 0.0, "perte_revenus": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.13, "tension_tresorerie": 0.02}</t>
   </si>
   <si>
     <t>{"0": 0.01, "1": 0.0, "2": 0.0, "3": 0.03, "4": 0.96}</t>
   </si>
   <si>
-    <t>{"en_cours": 0.0, "a_faire": 0.0, "escalade_contentieux": 0.0, "restructuration": 0.0, "regularise_a_verifier": 0.22, "promesse_reglement": 0.78}</t>
-  </si>
-  <si>
-    <t>{"publique": 0.07, "parapublique": 0.0, "particulier": 0.82, "privee": 0.11}</t>
-  </si>
-  <si>
-    <t>{"litige_juridique": 0.0, "aucun_motif": 0.0, "sante_deces": 0.0, "retard_technique": 0.14, "perte_revenus": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.0, "tension_tresorerie": 0.86}</t>
-  </si>
-  <si>
-    <t>{"0": 0.0, "1": 0.0, "2": 0.09, "3": 0.18, "4": 0.73}</t>
-  </si>
-  <si>
-    <t>{"escalade_contentieux": 0.01, "promesse_reglement": 0.62, "restructuration": 0.0, "en_cours": 0.29, "a_faire": 0.0, "regularise_a_verifier": 0.08}</t>
-  </si>
-  <si>
-    <t>{"publique": 0.0, "particulier": 0.62, "privee": 0.38, "parapublique": 0.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 1.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0, "aucun_motif": 0.0, "regularisation_annoncee": 0.0, "sante_deces": 0.0, "retard_technique": 0.0, "litige_juridique": 0.0, "perte_revenus": 0.0}</t>
-  </si>
-  <si>
-    <t>{"a_faire": 0.01, "regularise_a_verifier": 0.0, "en_cours": 0.7, "promesse_reglement": 0.0, "escalade_contentieux": 0.29, "restructuration": 0.0}</t>
-  </si>
-  <si>
-    <t>{"parapublique": 0.08, "privee": 0.01, "publique": 0.91, "particulier": 0.0}</t>
-  </si>
-  <si>
-    <t>{"tension_tresorerie": 0.0, "aucun_motif": 0.01, "retard_technique": 0.0, "perte_revenus": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.99, "litige_juridique": 0.0, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.23, "1": 0.77, "2": 0.0, "3": 0.0, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"en_cours": 0.0, "restructuration": 0.0, "a_faire": 0.0, "escalade_contentieux": 0.0, "regularise_a_verifier": 1.0, "promesse_reglement": 0.0}</t>
-  </si>
-  <si>
-    <t>{"privee": 0.99, "parapublique": 0.0, "particulier": 0.01, "publique": 0.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 0.0, "tension_tresorerie": 0.01, "regularisation_annoncee": 0.0, "retard_technique": 0.06, "perte_revenus": 0.93, "litige_juridique": 0.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "sante_deces": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.04, "1": 0.74, "2": 0.08, "3": 0.14, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"en_cours": 0.0, "promesse_reglement": 1.0, "a_faire": 0.0, "restructuration": 0.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.0}</t>
-  </si>
-  <si>
-    <t>{"particulier": 0.88, "parapublique": 0.0, "privee": 0.12, "publique": 0.0}</t>
-  </si>
-  <si>
-    <t>{"client_injoignable": 0.0, "sante_deces": 0.0, "regularisation_annoncee": 0.0, "retard_technique": 0.0, "perte_revenus": 1.0, "litige_juridique": 0.0, "aucun_motif": 0.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0}</t>
-  </si>
-  <si>
-    <t>{"0": 0.1, "1": 0.88, "2": 0.02, "3": 0.0, "4": 0.0}</t>
-  </si>
-  <si>
-    <t>{"en_cours": 0.0, "promesse_reglement": 0.0, "a_faire": 0.0, "restructuration": 1.0, "regularise_a_verifier": 0.0, "escalade_contentieux": 0.0}</t>
+    <t>{"particulier": 0.81, "privee": 0.12, "parapublique": 0.0, "publique": 0.07}</t>
+  </si>
+  <si>
+    <t>{"regularisation_annoncee": 0.0, "perte_revenus": 0.0, "fraude_detournement": 0.0, "litige_juridique": 0.0, "aucun_motif": 0.0, "retard_technique": 0.15, "sante_deces": 0.0, "client_injoignable": 0.0, "tension_tresorerie": 0.85}</t>
+  </si>
+  <si>
+    <t>{"0": 0.0, "1": 0.0, "2": 0.08, "3": 0.21, "4": 0.71}</t>
+  </si>
+  <si>
+    <t>{"escalade_contentieux": 0.01, "restructuration": 0.0, "regularise_a_verifier": 0.08, "en_cours": 0.32, "promesse_reglement": 0.59, "a_faire": 0.0}</t>
+  </si>
+  <si>
+    <t>{"publique": 0.0, "particulier": 0.67, "parapublique": 0.0, "privee": 0.33}</t>
+  </si>
+  <si>
+    <t>{"aucun_motif": 0.0, "client_injoignable": 1.0, "fraude_detournement": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "retard_technique": 0.0, "regularisation_annoncee": 0.0, "perte_revenus": 0.0, "sante_deces": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.8, "1": 0.2, "2": 0.0, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"regularise_a_verifier": 0.0, "a_faire": 0.01, "promesse_reglement": 0.0, "en_cours": 0.68, "restructuration": 0.0, "escalade_contentieux": 0.31}</t>
+  </si>
+  <si>
+    <t>{"particulier": 0.0, "parapublique": 0.09, "privee": 0.01, "publique": 0.9}</t>
+  </si>
+  <si>
+    <t>{"litige_juridique": 0.0, "aucun_motif": 0.01, "tension_tresorerie": 0.0, "fraude_detournement": 0.0, "regularisation_annoncee": 0.99, "retard_technique": 0.0, "perte_revenus": 0.0, "sante_deces": 0.0, "client_injoignable": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.27, "1": 0.73, "2": 0.0, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"escalade_contentieux": 0.0, "en_cours": 0.0, "restructuration": 0.0, "a_faire": 0.0, "regularise_a_verifier": 1.0, "promesse_reglement": 0.0}</t>
+  </si>
+  <si>
+    <t>{"privee": 0.97, "particulier": 0.03, "parapublique": 0.0, "publique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"sante_deces": 0.0, "litige_juridique": 0.0, "aucun_motif": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "perte_revenus": 0.92, "tension_tresorerie": 0.01, "regularisation_annoncee": 0.0, "retard_technique": 0.07}</t>
+  </si>
+  <si>
+    <t>{"0": 0.03, "1": 0.8, "2": 0.07, "3": 0.1, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"promesse_reglement": 1.0, "restructuration": 0.0, "a_faire": 0.0, "escalade_contentieux": 0.0, "regularise_a_verifier": 0.0, "en_cours": 0.0}</t>
+  </si>
+  <si>
+    <t>{"parapublique": 0.0, "particulier": 0.81, "privee": 0.19, "publique": 0.0}</t>
+  </si>
+  <si>
+    <t>{"aucun_motif": 0.0, "client_injoignable": 0.0, "fraude_detournement": 0.0, "retard_technique": 0.0, "tension_tresorerie": 0.0, "litige_juridique": 0.0, "regularisation_annoncee": 0.0, "perte_revenus": 1.0, "sante_deces": 0.0}</t>
+  </si>
+  <si>
+    <t>{"0": 0.09, "1": 0.9, "2": 0.01, "3": 0.0, "4": 0.0}</t>
+  </si>
+  <si>
+    <t>{"a_faire": 0.0, "escalade_contentieux": 0.0, "regularise_a_verifier": 0.0, "restructuration": 1.0, "en_cours": 0.0, "promesse_reglement": 0.0}</t>
   </si>
 </sst>
 </file>
@@ -2234,10 +2231,10 @@
                   <c:v>À faire</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Restructuration</c:v>
+                  <c:v>En cours</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>En cours</c:v>
+                  <c:v>Restructuration</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>Escalade contentieux</c:v>
@@ -2252,7 +2249,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>8</c:v>
@@ -2264,7 +2261,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>2</c:v>
@@ -3268,8 +3265,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Controle" displayName="Controle" ref="A6:H33" totalsRowShown="0">
-  <autoFilter ref="A6:H33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Controle" displayName="Controle" ref="A6:H31" totalsRowShown="0">
+  <autoFilter ref="A6:H31"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Réf LD" dataDxfId="0"/>
     <tableColumn id="2" name="Client" dataDxfId="1"/>
@@ -3691,7 +3688,7 @@
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7">
@@ -3870,7 +3867,7 @@
         <v>29</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
         <v>36</v>
@@ -4004,7 +4001,7 @@
         <v>33</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P6" t="s">
         <v>49</v>
@@ -4345,10 +4342,10 @@
         <v>31</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>20</v>
@@ -4482,10 +4479,10 @@
         <v>31</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>18</v>
@@ -4619,7 +4616,7 @@
         <v>31</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>29</v>
@@ -4848,7 +4845,7 @@
         <v>31</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M20" s="11" t="s">
         <v>29</v>
@@ -4951,21 +4948,21 @@
         <v>15</v>
       </c>
       <c r="O22" s="12" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>104</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23" s="13">
         <v>3778000</v>
@@ -4983,16 +4980,16 @@
         <v>46308</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>31</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N23" s="11" t="s">
         <v>17</v>
@@ -5001,10 +4998,10 @@
     </row>
     <row r="24" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>72</v>
@@ -5028,16 +5025,16 @@
         <v>46354</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>31</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>15</v>
@@ -5046,10 +5043,10 @@
     </row>
     <row r="25" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>86</v>
@@ -5073,13 +5070,13 @@
         <v>46345</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>31</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>29</v>
@@ -5088,15 +5085,15 @@
         <v>16</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>86</v>
@@ -5124,7 +5121,7 @@
         <v>31</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M26" s="11" t="s">
         <v>31</v>
@@ -5136,10 +5133,10 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>104</v>
@@ -5167,7 +5164,7 @@
         <v>31</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M27" s="11" t="s">
         <v>31</v>
@@ -5179,10 +5176,10 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>86</v>
@@ -5210,7 +5207,7 @@
         <v>31</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>31</v>
@@ -5222,10 +5219,10 @@
     </row>
     <row r="29" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>104</v>
@@ -5249,7 +5246,7 @@
         <v>46342</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>31</v>
@@ -5267,10 +5264,10 @@
     </row>
     <row r="30" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>72</v>
@@ -5294,7 +5291,7 @@
         <v>46333</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>31</v>
@@ -5312,10 +5309,10 @@
     </row>
     <row r="31" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>72</v>
@@ -5357,10 +5354,10 @@
     </row>
     <row r="32" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>104</v>
@@ -5399,7 +5396,7 @@
         <v>16</v>
       </c>
       <c r="O32" s="12" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.25">
@@ -5437,24 +5434,22 @@
         <v>31</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N33" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="O33" s="12" t="s">
-        <v>166</v>
-      </c>
+      <c r="O33" s="12"/>
     </row>
     <row r="34" spans="1:15" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B34" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>168</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>86</v>
@@ -5498,10 +5493,10 @@
     </row>
     <row r="35" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>86</v>
@@ -5543,10 +5538,10 @@
     </row>
     <row r="36" spans="1:15" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>171</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>172</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>104</v>
@@ -5576,10 +5571,10 @@
         <v>31</v>
       </c>
       <c r="L36" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M36" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N36" s="11" t="s">
         <v>18</v>
@@ -5682,7 +5677,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5699,7 +5694,7 @@
     </row>
     <row r="2" spans="1:13" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5773,25 +5768,25 @@
         <v>14</v>
       </c>
       <c r="F6" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>44</v>
       </c>
       <c r="I6" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="K6" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="L6" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="L6" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>68</v>
@@ -5814,10 +5809,10 @@
         <v>15</v>
       </c>
       <c r="F7" s="16">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="16">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>49</v>
@@ -5826,13 +5821,13 @@
         <v>0.96</v>
       </c>
       <c r="J7" s="16">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>30</v>
       </c>
       <c r="L7" s="16">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="M7" s="11" t="s">
         <v>30</v>
@@ -5855,16 +5850,16 @@
         <v>16</v>
       </c>
       <c r="F8" s="16">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="G8" s="16">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>49</v>
       </c>
       <c r="I8" s="16">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="J8" s="16">
         <v>0.04</v>
@@ -5905,19 +5900,19 @@
         <v>45</v>
       </c>
       <c r="I9" s="16">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="J9" s="16">
         <v>0.04</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L9" s="16">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="26" customHeight="1">
@@ -5937,7 +5932,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="16">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="G10" s="16">
         <v>0.03</v>
@@ -5946,10 +5941,10 @@
         <v>46</v>
       </c>
       <c r="I10" s="16">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="J10" s="16">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>89</v>
@@ -5978,7 +5973,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="16">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G11" s="16">
         <v>0.97</v>
@@ -5987,7 +5982,7 @@
         <v>46</v>
       </c>
       <c r="I11" s="16">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="J11" s="16">
         <v>0.06</v>
@@ -5996,7 +5991,7 @@
         <v>30</v>
       </c>
       <c r="L11" s="16">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="M11" s="11" t="s">
         <v>30</v>
@@ -6022,25 +6017,25 @@
         <v>1</v>
       </c>
       <c r="G12" s="16">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="16">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="J12" s="16">
         <v>0.04</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L12" s="16">
         <v>1</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="26" customHeight="1">
@@ -6060,7 +6055,7 @@
         <v>17</v>
       </c>
       <c r="F13" s="16">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="G13" s="16">
         <v>0.97</v>
@@ -6069,7 +6064,7 @@
         <v>46</v>
       </c>
       <c r="I13" s="16">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="J13" s="16">
         <v>0.05</v>
@@ -6151,16 +6146,16 @@
         <v>45</v>
       </c>
       <c r="I15" s="16">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="J15" s="16">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L15" s="16">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="M15" s="11" t="s">
         <v>29</v>
@@ -6186,7 +6181,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="16">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>48</v>
@@ -6242,7 +6237,7 @@
         <v>31</v>
       </c>
       <c r="L17" s="16">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="M17" s="11" t="s">
         <v>31</v>
@@ -6265,7 +6260,7 @@
         <v>17</v>
       </c>
       <c r="F18" s="16">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="G18" s="16">
         <v>0.03</v>
@@ -6347,10 +6342,10 @@
         <v>17</v>
       </c>
       <c r="F20" s="16">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G20" s="16">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>46</v>
@@ -6362,7 +6357,7 @@
         <v>0.04</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L20" s="16">
         <v>0.5</v>
@@ -6397,7 +6392,7 @@
         <v>47</v>
       </c>
       <c r="I21" s="16">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="J21" s="16">
         <v>0.05</v>
@@ -6432,22 +6427,22 @@
         <v>0.85</v>
       </c>
       <c r="G22" s="16">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>48</v>
       </c>
       <c r="I22" s="16">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="J22" s="16">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>30</v>
       </c>
       <c r="L22" s="16">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="M22" s="11" t="s">
         <v>29</v>
@@ -6455,57 +6450,57 @@
     </row>
     <row r="23" spans="1:13" ht="26" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E23" s="11" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="16">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G23" s="16">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>46</v>
       </c>
       <c r="I23" s="16">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J23" s="16">
         <v>0.04</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L23" s="16">
         <v>1</v>
       </c>
       <c r="M23" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="39" customHeight="1">
       <c r="A24" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>78</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E24" s="11" t="s">
         <v>15</v>
@@ -6520,39 +6515,39 @@
         <v>46</v>
       </c>
       <c r="I24" s="16">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="J24" s="16">
         <v>0.08</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L24" s="16">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="M24" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="26" customHeight="1">
       <c r="A25" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>93</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E25" s="11" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="16">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="G25" s="16">
         <v>0.05</v>
@@ -6561,16 +6556,16 @@
         <v>46</v>
       </c>
       <c r="I25" s="16">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="J25" s="16">
         <v>0.05</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L25" s="16">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="M25" s="11" t="s">
         <v>29</v>
@@ -6578,16 +6573,16 @@
     </row>
     <row r="26" spans="1:13" ht="26" customHeight="1">
       <c r="A26" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>93</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26" s="11" t="s">
         <v>16</v>
@@ -6596,16 +6591,16 @@
         <v>0.99</v>
       </c>
       <c r="G26" s="16">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>48</v>
       </c>
       <c r="I26" s="16">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="J26" s="16">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>30</v>
@@ -6619,16 +6614,16 @@
     </row>
     <row r="27" spans="1:13" ht="26" customHeight="1">
       <c r="A27" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>78</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>15</v>
@@ -6643,7 +6638,7 @@
         <v>48</v>
       </c>
       <c r="I27" s="16">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="J27" s="16">
         <v>0.05</v>
@@ -6652,7 +6647,7 @@
         <v>30</v>
       </c>
       <c r="L27" s="16">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="M27" s="11" t="s">
         <v>30</v>
@@ -6660,10 +6655,10 @@
     </row>
     <row r="28" spans="1:13" ht="26" customHeight="1">
       <c r="A28" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>73</v>
@@ -6675,25 +6670,25 @@
         <v>15</v>
       </c>
       <c r="F28" s="16">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="G28" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="H28" s="11" t="s">
         <v>49</v>
       </c>
       <c r="I28" s="16">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J28" s="16">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>30</v>
       </c>
       <c r="L28" s="16">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="M28" s="11" t="s">
         <v>30</v>
@@ -6701,10 +6696,10 @@
     </row>
     <row r="29" spans="1:13" ht="39" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>78</v>
@@ -6716,7 +6711,7 @@
         <v>16</v>
       </c>
       <c r="F29" s="16">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G29" s="16">
         <v>0.96</v>
@@ -6725,7 +6720,7 @@
         <v>49</v>
       </c>
       <c r="I29" s="16">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="J29" s="16">
         <v>0.06</v>
@@ -6734,7 +6729,7 @@
         <v>30</v>
       </c>
       <c r="L29" s="16">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="M29" s="11" t="s">
         <v>29</v>
@@ -6766,27 +6761,27 @@
         <v>45</v>
       </c>
       <c r="I30" s="16">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="J30" s="16">
         <v>0.04</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L30" s="16">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="26" customHeight="1">
       <c r="A31" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>168</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>78</v>
@@ -6807,10 +6802,10 @@
         <v>46</v>
       </c>
       <c r="I31" s="16">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="J31" s="16">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>89</v>
@@ -6824,10 +6819,10 @@
     </row>
     <row r="32" spans="1:13" ht="26" customHeight="1">
       <c r="A32" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>78</v>
@@ -6839,7 +6834,7 @@
         <v>18</v>
       </c>
       <c r="F32" s="16">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="G32" s="16">
         <v>0.97</v>
@@ -6848,10 +6843,10 @@
         <v>46</v>
       </c>
       <c r="I32" s="16">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="J32" s="16">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>30</v>
@@ -6865,10 +6860,10 @@
     </row>
     <row r="33" spans="1:13" ht="39" customHeight="1">
       <c r="A33" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33" s="12" t="s">
         <v>171</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>172</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>105</v>
@@ -6883,25 +6878,25 @@
         <v>1</v>
       </c>
       <c r="G33" s="16">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>46</v>
       </c>
       <c r="I33" s="16">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="J33" s="16">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L33" s="16">
         <v>1</v>
       </c>
       <c r="M33" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6998,7 +6993,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7012,7 +7007,7 @@
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7077,10 +7072,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="H6" s="10" t="s">
         <v>35</v>
@@ -7094,10 +7089,10 @@
     </row>
     <row r="7" spans="1:10" ht="26" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C7" s="13">
         <v>8984800</v>
@@ -7121,7 +7116,7 @@
         <v>48</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="39" customHeight="1">
@@ -7190,10 +7185,10 @@
     </row>
     <row r="10" spans="1:10" ht="39" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C10" s="13">
         <v>4935158</v>
@@ -7286,10 +7281,10 @@
     </row>
     <row r="13" spans="1:10" ht="26" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="13">
         <v>1630883</v>
@@ -7318,10 +7313,10 @@
     </row>
     <row r="14" spans="1:10" ht="26" customHeight="1">
       <c r="A14" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>169</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>170</v>
       </c>
       <c r="C14" s="13">
         <v>182902153</v>
@@ -7446,10 +7441,10 @@
     </row>
     <row r="18" spans="1:10" ht="26" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" s="13">
         <v>8643958</v>
@@ -7473,7 +7468,7 @@
         <v>48</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="26" customHeight="1">
@@ -7552,7 +7547,7 @@
     <tabColor rgb="FF005C83"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -7566,7 +7561,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7578,7 +7573,7 @@
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -7634,16 +7629,16 @@
         <v>60</v>
       </c>
       <c r="E6" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="G6" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="H6" s="10" t="s">
         <v>189</v>
-      </c>
-      <c r="H6" s="10" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="26" customHeight="1">
@@ -7663,13 +7658,13 @@
         <v>41</v>
       </c>
       <c r="F7" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H7" s="12" t="s">
         <v>191</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="26" customHeight="1">
@@ -7689,13 +7684,13 @@
         <v>41</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -7715,13 +7710,13 @@
         <v>42</v>
       </c>
       <c r="F9" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H9" s="12" t="s">
         <v>194</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -7741,13 +7736,13 @@
         <v>42</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -7767,13 +7762,13 @@
         <v>43</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -7793,13 +7788,13 @@
         <v>43</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -7819,13 +7814,13 @@
         <v>42</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -7845,13 +7840,13 @@
         <v>42</v>
       </c>
       <c r="F14" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H14" s="12" t="s">
         <v>191</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -7871,13 +7866,13 @@
         <v>43</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="26" customHeight="1">
@@ -7897,13 +7892,13 @@
         <v>42</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -7923,13 +7918,13 @@
         <v>41</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -7949,114 +7944,114 @@
         <v>41</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C19" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C20" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="26" customHeight="1">
+      <c r="A21" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H20" s="12" t="s">
+      <c r="D21" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="H21" s="12" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="26" customHeight="1">
       <c r="A22" s="11" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>205</v>
@@ -8064,10 +8059,10 @@
     </row>
     <row r="23" spans="1:8" ht="26" customHeight="1">
       <c r="A23" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>86</v>
@@ -8079,88 +8074,88 @@
         <v>40</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H23" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="26" customHeight="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B24" s="12" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="11" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="11" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>93</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>206</v>
@@ -8168,114 +8163,114 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="11" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="26" customHeight="1">
       <c r="A29" s="11" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>78</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F29" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="H29" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="G29" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+    </row>
+    <row r="30" spans="1:8" ht="26" customHeight="1">
       <c r="A30" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>86</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="26" customHeight="1">
       <c r="A31" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>167</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>168</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>86</v>
@@ -8287,65 +8282,13 @@
         <v>40</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="26" customHeight="1">
-      <c r="A32" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="26" customHeight="1">
-      <c r="A33" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H33" s="12" t="s">
-        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -8354,7 +8297,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="F4:H4"/>
   </mergeCells>
-  <conditionalFormatting sqref="F7:G33">
+  <conditionalFormatting sqref="F7:G31">
     <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"Oui"</formula>
     </cfRule>
@@ -8393,13 +8336,13 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -8429,18 +8372,18 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="10" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="51" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="21" customHeight="1">
@@ -8448,15 +8391,15 @@
         <v>64</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="36" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="36" customHeight="1">
@@ -8464,7 +8407,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="36" customHeight="1">
@@ -8472,39 +8415,39 @@
         <v>68</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="36" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="36" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="36" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="36" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -8543,7 +8486,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8553,7 +8496,7 @@
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8591,42 +8534,42 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" t="s">
         <v>237</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E5" t="s">
         <v>238</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F5" t="s">
         <v>239</v>
-      </c>
-      <c r="D5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E5" t="s">
-        <v>241</v>
-      </c>
-      <c r="F5" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="E6" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="F6" s="10" t="s">
         <v>233</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8634,19 +8577,19 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8654,16 +8597,16 @@
         <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D8">
         <v>0.04</v>
       </c>
       <c r="F8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8671,16 +8614,16 @@
         <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D9">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="F9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8688,19 +8631,19 @@
         <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E10">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8708,16 +8651,16 @@
         <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D11">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="F11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8725,10 +8668,10 @@
         <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C12" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D12">
         <v>3.95</v>
@@ -8737,7 +8680,7 @@
         <v>0.96</v>
       </c>
       <c r="F12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8745,16 +8688,16 @@
         <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D13">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F13" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8762,19 +8705,19 @@
         <v>70</v>
       </c>
       <c r="B14" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D14" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E14">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
       <c r="F14" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8782,19 +8725,19 @@
         <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C15" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D15" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8802,16 +8745,16 @@
         <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D16">
         <v>0.02</v>
       </c>
       <c r="F16" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -8819,16 +8762,16 @@
         <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C17" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D17">
         <v>0.05</v>
       </c>
       <c r="F17" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -8836,19 +8779,19 @@
         <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D18" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E18">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="F18" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -8856,16 +8799,16 @@
         <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D19">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="F19" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -8873,19 +8816,19 @@
         <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D20">
-        <v>3.61</v>
+        <v>3.57</v>
       </c>
       <c r="E20">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="F20" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -8893,16 +8836,16 @@
         <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C21" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D21">
         <v>0.04</v>
       </c>
       <c r="F21" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -8910,19 +8853,19 @@
         <v>75</v>
       </c>
       <c r="B22" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C22" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D22" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E22">
         <v>0.9399999999999999</v>
       </c>
       <c r="F22" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -8930,19 +8873,19 @@
         <v>80</v>
       </c>
       <c r="B23" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C23" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D23" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -8950,16 +8893,16 @@
         <v>80</v>
       </c>
       <c r="B24" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C24" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D24">
         <v>0.04</v>
       </c>
       <c r="F24" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -8967,16 +8910,16 @@
         <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C25" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D25">
         <v>0.05</v>
       </c>
       <c r="F25" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -8984,19 +8927,19 @@
         <v>80</v>
       </c>
       <c r="B26" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C26" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D26" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -9004,16 +8947,16 @@
         <v>80</v>
       </c>
       <c r="B27" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C27" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D27">
         <v>0.05</v>
       </c>
       <c r="F27" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -9021,19 +8964,19 @@
         <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C28" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D28">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="E28">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="F28" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -9041,16 +8984,16 @@
         <v>80</v>
       </c>
       <c r="B29" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C29" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D29">
         <v>0.04</v>
       </c>
       <c r="F29" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -9058,19 +9001,19 @@
         <v>80</v>
       </c>
       <c r="B30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D30" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E30">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="F30" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -9078,19 +9021,19 @@
         <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C31" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D31" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E31">
         <v>0.98</v>
       </c>
       <c r="F31" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -9098,16 +9041,16 @@
         <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D32">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F32" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -9115,16 +9058,16 @@
         <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C33" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D33">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="F33" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -9132,19 +9075,19 @@
         <v>84</v>
       </c>
       <c r="B34" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C34" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D34" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E34">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="F34" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -9152,16 +9095,16 @@
         <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C35" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D35">
         <v>0.03</v>
       </c>
       <c r="F35" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -9169,19 +9112,19 @@
         <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C36" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D36">
+        <v>0.8</v>
+      </c>
+      <c r="E36">
         <v>0.83</v>
       </c>
-      <c r="E36">
-        <v>0.85</v>
-      </c>
       <c r="F36" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -9189,16 +9132,16 @@
         <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C37" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D37">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="F37" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -9206,19 +9149,19 @@
         <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C38" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D38" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -9226,19 +9169,19 @@
         <v>91</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C39" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D39" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E39">
         <v>0.99</v>
       </c>
       <c r="F39" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -9246,16 +9189,16 @@
         <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C40" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D40">
         <v>0.95</v>
       </c>
       <c r="F40" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -9263,16 +9206,16 @@
         <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D41">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="F41" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -9280,19 +9223,19 @@
         <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C42" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D42" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E42">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -9300,16 +9243,16 @@
         <v>91</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C43" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D43">
         <v>0.97</v>
       </c>
       <c r="F43" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -9317,19 +9260,19 @@
         <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C44" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D44">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="E44">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="F44" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -9337,16 +9280,16 @@
         <v>91</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C45" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D45">
         <v>0.06</v>
       </c>
       <c r="F45" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -9354,19 +9297,19 @@
         <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D46" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F46" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -9374,19 +9317,19 @@
         <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C47" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D47" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E47">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F47" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -9394,16 +9337,16 @@
         <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C48" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D48">
         <v>0.24</v>
       </c>
       <c r="F48" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -9411,16 +9354,16 @@
         <v>95</v>
       </c>
       <c r="B49" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C49" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D49">
         <v>0.07000000000000001</v>
       </c>
       <c r="F49" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -9428,19 +9371,19 @@
         <v>95</v>
       </c>
       <c r="B50" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C50" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D50" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -9448,16 +9391,16 @@
         <v>95</v>
       </c>
       <c r="B51" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D51">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="F51" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -9465,19 +9408,19 @@
         <v>95</v>
       </c>
       <c r="B52" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C52" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D52">
+        <v>0.85</v>
+      </c>
+      <c r="E52">
         <v>0.86</v>
       </c>
-      <c r="E52">
-        <v>0.87</v>
-      </c>
       <c r="F52" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -9485,16 +9428,16 @@
         <v>95</v>
       </c>
       <c r="B53" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C53" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D53">
         <v>0.04</v>
       </c>
       <c r="F53" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -9502,19 +9445,19 @@
         <v>95</v>
       </c>
       <c r="B54" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C54" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -9522,19 +9465,19 @@
         <v>98</v>
       </c>
       <c r="B55" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C55" t="s">
-        <v>244</v>
-      </c>
-      <c r="D55" t="s">
-        <v>290</v>
+        <v>253</v>
+      </c>
+      <c r="D55">
+        <v>0.99</v>
       </c>
       <c r="E55">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="F55" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -9542,16 +9485,16 @@
         <v>98</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C56" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D56">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F56" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -9559,16 +9502,19 @@
         <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C57" t="s">
-        <v>248</v>
-      </c>
-      <c r="D57">
-        <v>0.58</v>
+        <v>241</v>
+      </c>
+      <c r="D57" t="s">
+        <v>257</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>249</v>
+        <v>289</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -9576,19 +9522,19 @@
         <v>98</v>
       </c>
       <c r="B58" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="C58" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D58" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E58">
-        <v>0.91</v>
+        <v>0.47</v>
       </c>
       <c r="F58" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -9596,16 +9542,16 @@
         <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D59">
-        <v>0.97</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F59" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -9613,19 +9559,16 @@
         <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C60" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D60">
-        <v>0.98</v>
-      </c>
-      <c r="E60">
-        <v>0.98</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F60" t="s">
-        <v>294</v>
+        <v>246</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -9633,16 +9576,19 @@
         <v>98</v>
       </c>
       <c r="B61" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
-      </c>
-      <c r="D61">
-        <v>0.05</v>
+        <v>241</v>
+      </c>
+      <c r="D61" t="s">
+        <v>292</v>
+      </c>
+      <c r="E61">
+        <v>0.92</v>
       </c>
       <c r="F61" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -9650,19 +9596,16 @@
         <v>98</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="C62" t="s">
-        <v>244</v>
-      </c>
-      <c r="D62" t="s">
-        <v>260</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="D62">
+        <v>0.97</v>
       </c>
       <c r="F62" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -9670,10 +9613,10 @@
         <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C63" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D63" t="s">
         <v>290</v>
@@ -9682,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -9690,16 +9633,16 @@
         <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D64">
         <v>0.03</v>
       </c>
       <c r="F64" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -9707,16 +9650,16 @@
         <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C65" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D65">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F65" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -9724,19 +9667,19 @@
         <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C66" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D66" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E66">
         <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -9744,16 +9687,16 @@
         <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D67">
         <v>0.03</v>
       </c>
       <c r="F67" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -9761,10 +9704,10 @@
         <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C68" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D68">
         <v>0.01</v>
@@ -9773,7 +9716,7 @@
         <v>0.99</v>
       </c>
       <c r="F68" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -9781,16 +9724,16 @@
         <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C69" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D69">
         <v>0.05</v>
       </c>
       <c r="F69" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -9798,19 +9741,19 @@
         <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C70" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D70" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E70">
         <v>0.99</v>
       </c>
       <c r="F70" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -9818,19 +9761,19 @@
         <v>107</v>
       </c>
       <c r="B71" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C71" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D71" t="s">
         <v>290</v>
       </c>
       <c r="E71">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="F71" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -9838,16 +9781,16 @@
         <v>107</v>
       </c>
       <c r="B72" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C72" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D72">
         <v>0.04</v>
       </c>
       <c r="F72" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -9855,16 +9798,16 @@
         <v>107</v>
       </c>
       <c r="B73" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C73" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D73">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="F73" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -9872,19 +9815,19 @@
         <v>107</v>
       </c>
       <c r="B74" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C74" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D74" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E74">
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -9892,16 +9835,16 @@
         <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C75" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D75">
         <v>0.04</v>
       </c>
       <c r="F75" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -9909,19 +9852,19 @@
         <v>107</v>
       </c>
       <c r="B76" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C76" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D76">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="E76">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="F76" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -9929,16 +9872,16 @@
         <v>107</v>
       </c>
       <c r="B77" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C77" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D77">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F77" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -9946,19 +9889,19 @@
         <v>107</v>
       </c>
       <c r="B78" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C78" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D78" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E78">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="F78" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -9966,19 +9909,19 @@
         <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C79" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D79" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -9986,16 +9929,16 @@
         <v>112</v>
       </c>
       <c r="B80" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C80" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D80">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F80" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -10003,16 +9946,16 @@
         <v>112</v>
       </c>
       <c r="B81" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C81" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D81">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="F81" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -10020,19 +9963,19 @@
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C82" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D82" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -10040,16 +9983,16 @@
         <v>112</v>
       </c>
       <c r="B83" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C83" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D83">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="F83" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -10057,10 +10000,10 @@
         <v>112</v>
       </c>
       <c r="B84" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C84" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D84">
         <v>3.07</v>
@@ -10069,7 +10012,7 @@
         <v>0.58</v>
       </c>
       <c r="F84" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -10077,16 +10020,16 @@
         <v>112</v>
       </c>
       <c r="B85" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C85" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D85">
         <v>0.06</v>
       </c>
       <c r="F85" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -10094,19 +10037,19 @@
         <v>112</v>
       </c>
       <c r="B86" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C86" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D86" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E86">
         <v>0.9399999999999999</v>
       </c>
       <c r="F86" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -10114,19 +10057,19 @@
         <v>115</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C87" t="s">
-        <v>256</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
+        <v>241</v>
+      </c>
+      <c r="D87" t="s">
+        <v>277</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="F87" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -10134,16 +10077,16 @@
         <v>115</v>
       </c>
       <c r="B88" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C88" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D88">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="F88" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -10151,19 +10094,16 @@
         <v>115</v>
       </c>
       <c r="B89" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C89" t="s">
-        <v>244</v>
-      </c>
-      <c r="D89" t="s">
-        <v>312</v>
-      </c>
-      <c r="E89">
-        <v>0.98</v>
+        <v>245</v>
+      </c>
+      <c r="D89">
+        <v>0.29</v>
       </c>
       <c r="F89" t="s">
-        <v>313</v>
+        <v>246</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -10171,19 +10111,19 @@
         <v>115</v>
       </c>
       <c r="B90" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C90" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D90" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="E90">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -10191,16 +10131,16 @@
         <v>115</v>
       </c>
       <c r="B91" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C91" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D91">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="F91" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -10208,16 +10148,19 @@
         <v>115</v>
       </c>
       <c r="B92" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C92" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D92">
-        <v>0.29</v>
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -10225,19 +10168,16 @@
         <v>115</v>
       </c>
       <c r="B93" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C93" t="s">
-        <v>244</v>
-      </c>
-      <c r="D93" t="s">
-        <v>292</v>
-      </c>
-      <c r="E93">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="D93">
+        <v>0.13</v>
       </c>
       <c r="F93" t="s">
-        <v>315</v>
+        <v>246</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -10245,16 +10185,19 @@
         <v>115</v>
       </c>
       <c r="B94" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C94" t="s">
-        <v>248</v>
-      </c>
-      <c r="D94">
-        <v>0.03</v>
+        <v>241</v>
+      </c>
+      <c r="D94" t="s">
+        <v>312</v>
+      </c>
+      <c r="E94">
+        <v>0.97</v>
       </c>
       <c r="F94" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -10262,16 +10205,19 @@
         <v>118</v>
       </c>
       <c r="B95" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C95" t="s">
-        <v>248</v>
-      </c>
-      <c r="D95">
-        <v>0.03</v>
+        <v>241</v>
+      </c>
+      <c r="D95" t="s">
+        <v>290</v>
+      </c>
+      <c r="E95">
+        <v>0.99</v>
       </c>
       <c r="F95" t="s">
-        <v>249</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -10279,19 +10225,16 @@
         <v>118</v>
       </c>
       <c r="B96" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C96" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D96">
-        <v>0</v>
-      </c>
-      <c r="E96">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="F96" t="s">
-        <v>311</v>
+        <v>246</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -10299,16 +10242,16 @@
         <v>118</v>
       </c>
       <c r="B97" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="C97" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D97">
-        <v>0.98</v>
+        <v>0.09</v>
       </c>
       <c r="F97" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -10316,19 +10259,19 @@
         <v>118</v>
       </c>
       <c r="B98" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="C98" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D98" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="E98">
-        <v>0.98</v>
+        <v>0.78</v>
       </c>
       <c r="F98" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -10336,19 +10279,16 @@
         <v>118</v>
       </c>
       <c r="B99" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C99" t="s">
-        <v>244</v>
-      </c>
-      <c r="D99" t="s">
-        <v>290</v>
-      </c>
-      <c r="E99">
-        <v>0.99</v>
+        <v>245</v>
+      </c>
+      <c r="D99">
+        <v>0.03</v>
       </c>
       <c r="F99" t="s">
-        <v>317</v>
+        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -10356,16 +10296,19 @@
         <v>118</v>
       </c>
       <c r="B100" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C100" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D100">
-        <v>0.07000000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -10373,16 +10316,16 @@
         <v>118</v>
       </c>
       <c r="B101" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C101" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D101">
-        <v>0.09</v>
+        <v>0.98</v>
       </c>
       <c r="F101" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -10390,19 +10333,19 @@
         <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C102" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D102" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="E102">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="F102" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -10410,19 +10353,19 @@
         <v>121</v>
       </c>
       <c r="B103" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C103" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D103" t="s">
-        <v>279</v>
+        <v>317</v>
       </c>
       <c r="E103">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -10430,16 +10373,16 @@
         <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C104" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D104">
-        <v>0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F104" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -10447,16 +10390,19 @@
         <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C105" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D105">
-        <v>0.86</v>
+        <v>0</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>249</v>
+        <v>311</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -10464,19 +10410,16 @@
         <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C106" t="s">
-        <v>244</v>
-      </c>
-      <c r="D106" t="s">
-        <v>320</v>
-      </c>
-      <c r="E106">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="D106">
+        <v>0.07000000000000001</v>
       </c>
       <c r="F106" t="s">
-        <v>321</v>
+        <v>246</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -10484,16 +10427,19 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C107" t="s">
-        <v>248</v>
-      </c>
-      <c r="D107">
-        <v>0.04</v>
+        <v>241</v>
+      </c>
+      <c r="D107" t="s">
+        <v>298</v>
+      </c>
+      <c r="E107">
+        <v>0.99</v>
       </c>
       <c r="F107" t="s">
-        <v>249</v>
+        <v>319</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -10501,19 +10447,19 @@
         <v>121</v>
       </c>
       <c r="B108" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C108" t="s">
-        <v>256</v>
-      </c>
-      <c r="D108">
-        <v>0</v>
+        <v>241</v>
+      </c>
+      <c r="D108" t="s">
+        <v>277</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="F108" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -10521,16 +10467,16 @@
         <v>121</v>
       </c>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C109" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D109">
         <v>0.07000000000000001</v>
       </c>
       <c r="F109" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -10538,19 +10484,16 @@
         <v>121</v>
       </c>
       <c r="B110" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C110" t="s">
-        <v>244</v>
-      </c>
-      <c r="D110" t="s">
-        <v>300</v>
-      </c>
-      <c r="E110">
-        <v>0.99</v>
+        <v>245</v>
+      </c>
+      <c r="D110">
+        <v>0.86</v>
       </c>
       <c r="F110" t="s">
-        <v>322</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -10558,19 +10501,19 @@
         <v>124</v>
       </c>
       <c r="B111" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C111" t="s">
-        <v>256</v>
-      </c>
-      <c r="D111">
-        <v>1</v>
+        <v>241</v>
+      </c>
+      <c r="D111" t="s">
+        <v>242</v>
       </c>
       <c r="E111">
-        <v>0.97</v>
+        <v>0.87</v>
       </c>
       <c r="F111" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -10578,16 +10521,16 @@
         <v>124</v>
       </c>
       <c r="B112" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="C112" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D112">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F112" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -10595,19 +10538,16 @@
         <v>124</v>
       </c>
       <c r="B113" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="C113" t="s">
-        <v>244</v>
-      </c>
-      <c r="D113" t="s">
-        <v>271</v>
-      </c>
-      <c r="E113">
-        <v>0.5</v>
+        <v>245</v>
+      </c>
+      <c r="D113">
+        <v>0.67</v>
       </c>
       <c r="F113" t="s">
-        <v>324</v>
+        <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -10615,19 +10555,19 @@
         <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C114" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D114" t="s">
-        <v>245</v>
+        <v>292</v>
       </c>
       <c r="E114">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="F114" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -10635,16 +10575,16 @@
         <v>124</v>
       </c>
       <c r="B115" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C115" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D115">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="F115" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -10652,16 +10592,19 @@
         <v>124</v>
       </c>
       <c r="B116" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C116" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D116">
-        <v>0.62</v>
+        <v>1.01</v>
+      </c>
+      <c r="E116">
+        <v>0.97</v>
       </c>
       <c r="F116" t="s">
-        <v>249</v>
+        <v>323</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -10669,19 +10612,16 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C117" t="s">
-        <v>244</v>
-      </c>
-      <c r="D117" t="s">
-        <v>292</v>
-      </c>
-      <c r="E117">
-        <v>0.84</v>
+        <v>245</v>
+      </c>
+      <c r="D117">
+        <v>0.04</v>
       </c>
       <c r="F117" t="s">
-        <v>326</v>
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -10689,16 +10629,19 @@
         <v>124</v>
       </c>
       <c r="B118" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C118" t="s">
-        <v>248</v>
-      </c>
-      <c r="D118">
-        <v>0.57</v>
+        <v>241</v>
+      </c>
+      <c r="D118" t="s">
+        <v>269</v>
+      </c>
+      <c r="E118">
+        <v>0.5</v>
       </c>
       <c r="F118" t="s">
-        <v>249</v>
+        <v>324</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -10706,19 +10649,19 @@
         <v>128</v>
       </c>
       <c r="B119" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C119" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D119" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E119">
         <v>0.99</v>
       </c>
       <c r="F119" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -10726,16 +10669,16 @@
         <v>128</v>
       </c>
       <c r="B120" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C120" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D120">
         <v>0.05</v>
       </c>
       <c r="F120" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -10743,16 +10686,16 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C121" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D121">
         <v>0.26</v>
       </c>
       <c r="F121" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -10760,19 +10703,19 @@
         <v>128</v>
       </c>
       <c r="B122" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C122" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D122" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E122">
         <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -10780,16 +10723,16 @@
         <v>128</v>
       </c>
       <c r="B123" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C123" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D123">
         <v>0.96</v>
       </c>
       <c r="F123" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -10797,19 +10740,19 @@
         <v>128</v>
       </c>
       <c r="B124" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C124" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D124">
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="E124">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="F124" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -10817,16 +10760,16 @@
         <v>128</v>
       </c>
       <c r="B125" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C125" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D125">
         <v>0.05</v>
       </c>
       <c r="F125" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -10834,19 +10777,19 @@
         <v>128</v>
       </c>
       <c r="B126" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C126" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D126" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E126">
         <v>0.98</v>
       </c>
       <c r="F126" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -10854,19 +10797,19 @@
         <v>132</v>
       </c>
       <c r="B127" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C127" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D127" t="s">
         <v>290</v>
       </c>
       <c r="E127">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="F127" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -10874,16 +10817,16 @@
         <v>132</v>
       </c>
       <c r="B128" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C128" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D128">
         <v>0.05</v>
       </c>
       <c r="F128" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -10891,16 +10834,16 @@
         <v>132</v>
       </c>
       <c r="B129" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C129" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D129">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F129" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -10908,19 +10851,19 @@
         <v>132</v>
       </c>
       <c r="B130" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C130" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D130" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E130">
         <v>0.85</v>
       </c>
       <c r="F130" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -10928,16 +10871,16 @@
         <v>132</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C131" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D131">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F131" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -10945,19 +10888,19 @@
         <v>132</v>
       </c>
       <c r="B132" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C132" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D132">
-        <v>3.08</v>
+        <v>3.15</v>
       </c>
       <c r="E132">
-        <v>0.74</v>
+        <v>0.67</v>
       </c>
       <c r="F132" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -10965,16 +10908,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C133" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D133">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="F133" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -10982,528 +10925,528 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C134" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D134" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E134">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="F134" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B135" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C135" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D135" t="s">
         <v>290</v>
       </c>
       <c r="E135">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="F135" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B136" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C136" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D136">
         <v>0.05</v>
       </c>
       <c r="F136" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C137" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D137">
         <v>0.08</v>
       </c>
       <c r="F137" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C138" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D138" t="s">
         <v>292</v>
       </c>
       <c r="E138">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F138" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C139" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D139">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="F139" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C140" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D140">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="E140">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F140" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C141" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D141">
         <v>0.04</v>
       </c>
       <c r="F141" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C142" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D142" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E142">
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B143" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C143" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D143" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E143">
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B144" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C144" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D144">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="F144" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B145" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C145" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D145">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="F145" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B146" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C146" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D146" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E146">
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B147" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C147" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D147">
         <v>0.04</v>
       </c>
       <c r="F147" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B148" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C148" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D148">
         <v>0.98</v>
       </c>
       <c r="E148">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="F148" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B149" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C149" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D149">
         <v>0.08</v>
       </c>
       <c r="F149" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B150" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C150" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D150" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E150">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="F150" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B151" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C151" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D151" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="E151">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="F151" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B152" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C152" t="s">
-        <v>248</v>
-      </c>
-      <c r="D152">
-        <v>0.07000000000000001</v>
+        <v>241</v>
+      </c>
+      <c r="D152" t="s">
+        <v>242</v>
+      </c>
+      <c r="E152">
+        <v>0.8100000000000001</v>
       </c>
       <c r="F152" t="s">
-        <v>249</v>
+        <v>341</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B153" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C153" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D153">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F153" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B154" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C154" t="s">
-        <v>244</v>
-      </c>
-      <c r="D154" t="s">
-        <v>264</v>
-      </c>
-      <c r="E154">
-        <v>0.34</v>
+        <v>245</v>
+      </c>
+      <c r="D154">
+        <v>0.19</v>
       </c>
       <c r="F154" t="s">
-        <v>344</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B155" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C155" t="s">
-        <v>248</v>
-      </c>
-      <c r="D155">
-        <v>0.05</v>
+        <v>241</v>
+      </c>
+      <c r="D155" t="s">
+        <v>261</v>
+      </c>
+      <c r="E155">
+        <v>0.36</v>
       </c>
       <c r="F155" t="s">
-        <v>249</v>
+        <v>342</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B156" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C156" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="D156">
-        <v>1.11</v>
-      </c>
-      <c r="E156">
-        <v>0.55</v>
+        <v>0.05</v>
       </c>
       <c r="F156" t="s">
-        <v>345</v>
+        <v>246</v>
       </c>
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B157" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="C157" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D157">
-        <v>0.05</v>
+        <v>1.08</v>
+      </c>
+      <c r="E157">
+        <v>0.57</v>
       </c>
       <c r="F157" t="s">
-        <v>249</v>
+        <v>343</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B158" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C158" t="s">
-        <v>244</v>
-      </c>
-      <c r="D158" t="s">
-        <v>271</v>
-      </c>
-      <c r="E158">
-        <v>0.67</v>
+        <v>245</v>
+      </c>
+      <c r="D158">
+        <v>0.05</v>
       </c>
       <c r="F158" t="s">
-        <v>346</v>
+        <v>246</v>
       </c>
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B159" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C159" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E159">
         <v>0.99</v>
       </c>
       <c r="F159" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B160" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C160" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D160">
         <v>0.05</v>
       </c>
       <c r="F160" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B161" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C161" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D161">
         <v>0.76</v>
       </c>
       <c r="F161" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B162" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C162" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D162" t="s">
         <v>290</v>
@@ -11512,106 +11455,106 @@
         <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B163" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C163" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D163">
         <v>0.04</v>
       </c>
       <c r="F163" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B164" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C164" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D164">
         <v>0.08</v>
       </c>
       <c r="F164" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B165" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C165" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D165" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E165">
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B166" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C166" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D166">
         <v>0.04</v>
       </c>
       <c r="F166" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B167" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C167" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D167">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F167" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B168" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C168" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D168" t="s">
         <v>290</v>
@@ -11620,579 +11563,579 @@
         <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B169" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C169" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D169">
         <v>0.04</v>
       </c>
       <c r="F169" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B170" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C170" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D170">
         <v>0.1</v>
       </c>
       <c r="F170" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B171" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C171" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D171" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E171">
         <v>0.99</v>
       </c>
       <c r="F171" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B172" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C172" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D172">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="F172" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B173" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C173" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D173">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="E173">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="F173" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B174" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C174" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D174">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F174" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B175" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C175" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D175" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E175">
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B176" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C176" t="s">
-        <v>244</v>
-      </c>
-      <c r="D176" t="s">
-        <v>279</v>
-      </c>
-      <c r="E176">
-        <v>0.91</v>
+        <v>245</v>
+      </c>
+      <c r="D176">
+        <v>0.13</v>
       </c>
       <c r="F176" t="s">
-        <v>353</v>
+        <v>246</v>
       </c>
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B177" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C177" t="s">
-        <v>248</v>
-      </c>
-      <c r="D177">
-        <v>0.9399999999999999</v>
+        <v>241</v>
+      </c>
+      <c r="D177" t="s">
+        <v>249</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>249</v>
+        <v>351</v>
       </c>
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B178" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C178" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D178">
-        <v>0.13</v>
+        <v>0.95</v>
       </c>
       <c r="F178" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B179" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C179" t="s">
-        <v>244</v>
-      </c>
-      <c r="D179" t="s">
-        <v>252</v>
+        <v>253</v>
+      </c>
+      <c r="D179">
+        <v>2.75</v>
       </c>
       <c r="E179">
-        <v>1</v>
+        <v>0.79</v>
       </c>
       <c r="F179" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B180" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C180" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D180">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="F180" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B181" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C181" t="s">
-        <v>256</v>
-      </c>
-      <c r="D181">
-        <v>2.79</v>
+        <v>241</v>
+      </c>
+      <c r="D181" t="s">
+        <v>257</v>
       </c>
       <c r="E181">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="F181" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B182" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="C182" t="s">
-        <v>248</v>
-      </c>
-      <c r="D182">
-        <v>0.05</v>
+        <v>241</v>
+      </c>
+      <c r="D182" t="s">
+        <v>277</v>
+      </c>
+      <c r="E182">
+        <v>0.89</v>
       </c>
       <c r="F182" t="s">
-        <v>249</v>
+        <v>354</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B183" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="C183" t="s">
-        <v>244</v>
-      </c>
-      <c r="D183" t="s">
-        <v>260</v>
-      </c>
-      <c r="E183">
-        <v>0.66</v>
+        <v>245</v>
+      </c>
+      <c r="D183">
+        <v>0.93</v>
       </c>
       <c r="F183" t="s">
-        <v>356</v>
+        <v>246</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B184" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C184" t="s">
-        <v>244</v>
-      </c>
-      <c r="D184" t="s">
-        <v>279</v>
-      </c>
-      <c r="E184">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="D184">
+        <v>0.1</v>
       </c>
       <c r="F184" t="s">
-        <v>357</v>
+        <v>246</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B185" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C185" t="s">
-        <v>248</v>
-      </c>
-      <c r="D185">
-        <v>0.07000000000000001</v>
+        <v>241</v>
+      </c>
+      <c r="D185" t="s">
+        <v>257</v>
+      </c>
+      <c r="E185">
+        <v>0.71</v>
       </c>
       <c r="F185" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B186" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="C186" t="s">
-        <v>248</v>
-      </c>
-      <c r="D186">
-        <v>0.07000000000000001</v>
+        <v>241</v>
+      </c>
+      <c r="D186" t="s">
+        <v>277</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>249</v>
+        <v>356</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B187" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C187" t="s">
-        <v>244</v>
-      </c>
-      <c r="D187" t="s">
-        <v>252</v>
-      </c>
-      <c r="E187">
-        <v>0.83</v>
+        <v>245</v>
+      </c>
+      <c r="D187">
+        <v>0.06</v>
       </c>
       <c r="F187" t="s">
-        <v>358</v>
+        <v>246</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B188" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C188" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D188">
-        <v>0.96</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F188" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B189" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C189" t="s">
-        <v>256</v>
-      </c>
-      <c r="D189">
-        <v>3.91</v>
+        <v>241</v>
+      </c>
+      <c r="D189" t="s">
+        <v>249</v>
       </c>
       <c r="E189">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="F189" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B190" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C190" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D190">
-        <v>0.09</v>
+        <v>0.97</v>
       </c>
       <c r="F190" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B191" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="C191" t="s">
-        <v>244</v>
-      </c>
-      <c r="D191" t="s">
-        <v>260</v>
+        <v>253</v>
+      </c>
+      <c r="D191">
+        <v>3.93</v>
       </c>
       <c r="E191">
-        <v>0.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F191" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B192" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C192" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D192" t="s">
         <v>290</v>
       </c>
       <c r="E192">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="F192" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B193" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C193" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D193">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F193" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B194" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C194" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D194">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="F194" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B195" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C195" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D195" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E195">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="F195" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B196" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C196" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D196">
         <v>0.96</v>
       </c>
       <c r="F196" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B197" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C197" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D197">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="E197">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="F197" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B198" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C198" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D198">
         <v>0.06</v>
       </c>
       <c r="F198" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B199" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C199" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D199" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E199">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="F199" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -12200,19 +12143,19 @@
         <v>164</v>
       </c>
       <c r="B200" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C200" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D200" t="s">
         <v>290</v>
       </c>
       <c r="E200">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F200" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -12220,16 +12163,16 @@
         <v>164</v>
       </c>
       <c r="B201" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C201" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D201">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F201" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -12237,16 +12180,16 @@
         <v>164</v>
       </c>
       <c r="B202" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C202" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D202">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="F202" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -12254,19 +12197,19 @@
         <v>164</v>
       </c>
       <c r="B203" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C203" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D203" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E203">
         <v>1</v>
       </c>
       <c r="F203" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -12274,16 +12217,16 @@
         <v>164</v>
       </c>
       <c r="B204" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C204" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D204">
         <v>0.05</v>
       </c>
       <c r="F204" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -12291,19 +12234,19 @@
         <v>164</v>
       </c>
       <c r="B205" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C205" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D205">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="E205">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="F205" t="s">
-        <v>270</v>
+        <v>365</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -12311,16 +12254,16 @@
         <v>164</v>
       </c>
       <c r="B206" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C206" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D206">
         <v>0.04</v>
       </c>
       <c r="F206" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -12328,463 +12271,463 @@
         <v>164</v>
       </c>
       <c r="B207" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C207" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D207" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E207">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="F207" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B208" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C208" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D208" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E208">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="F208" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B209" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C209" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D209">
         <v>0.03</v>
       </c>
       <c r="F209" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B210" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C210" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D210">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="F210" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B211" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C211" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D211" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E211">
         <v>0.99</v>
       </c>
       <c r="F211" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B212" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C212" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D212">
         <v>0.03</v>
       </c>
       <c r="F212" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B213" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C213" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D213">
+        <v>0.73</v>
+      </c>
+      <c r="E213">
         <v>0.77</v>
       </c>
-      <c r="E213">
-        <v>0.8</v>
-      </c>
       <c r="F213" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B214" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C214" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D214">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="F214" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B215" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C215" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D215" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E215">
         <v>1</v>
       </c>
       <c r="F215" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B216" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C216" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D216" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E216">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="F216" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B217" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C217" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D217">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F217" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B218" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C218" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D218">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F218" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B219" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C219" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D219" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E219">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="F219" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B220" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C220" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D220">
         <v>0.97</v>
       </c>
       <c r="F220" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B221" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C221" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D221">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="E221">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="F221" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B222" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C222" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D222">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F222" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B223" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C223" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D223" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E223">
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B224" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C224" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D224" t="s">
         <v>290</v>
       </c>
       <c r="E224">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="F224" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B225" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C225" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D225">
         <v>0.04</v>
       </c>
       <c r="F225" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B226" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C226" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D226">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="F226" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B227" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C227" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D227" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E227">
         <v>1</v>
       </c>
       <c r="F227" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B228" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C228" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D228">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="F228" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B229" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C229" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D229">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="E229">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="F229" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B230" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C230" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="D230">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F230" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B231" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C231" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="D231" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E231">
         <v>1</v>
       </c>
       <c r="F231" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
